--- a/Result/profitability/4406.xlsx
+++ b/Result/profitability/4406.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AM74"/>
+  <dimension ref="A1:AM75"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -669,10 +669,10 @@
         <v>-0.08</v>
       </c>
       <c r="M2" t="n">
-        <v>-0.2375</v>
+        <v>-0.1925</v>
       </c>
       <c r="N2" t="n">
-        <v>-4.18875</v>
+        <v>-3.42</v>
       </c>
       <c r="O2" t="n">
         <v>1</v>
@@ -780,10 +780,10 @@
         <v>0.22</v>
       </c>
       <c r="M3" t="n">
-        <v>-0.15125</v>
+        <v>-0.17</v>
       </c>
       <c r="N3" t="n">
-        <v>-2.3775</v>
+        <v>-2.51375</v>
       </c>
       <c r="O3" t="n">
         <v>1</v>
@@ -899,10 +899,10 @@
         <v>0.07000000000000001</v>
       </c>
       <c r="M4" t="n">
-        <v>-0.1475</v>
+        <v>-0.15625</v>
       </c>
       <c r="N4" t="n">
-        <v>-1.69375</v>
+        <v>-1.9925</v>
       </c>
       <c r="O4" t="n">
         <v>1</v>
@@ -1018,10 +1018,10 @@
         <v>-0.42</v>
       </c>
       <c r="M5" t="n">
-        <v>-0.195</v>
+        <v>-0.1225</v>
       </c>
       <c r="N5" t="n">
-        <v>-2.58</v>
+        <v>-2.55875</v>
       </c>
       <c r="O5" t="n">
         <v>0</v>
@@ -1137,10 +1137,10 @@
         <v>0.05</v>
       </c>
       <c r="M6" t="n">
-        <v>-0.1025</v>
+        <v>-0.09375</v>
       </c>
       <c r="N6" t="n">
-        <v>-1.5175</v>
+        <v>-0.3650000000000002</v>
       </c>
       <c r="O6" t="n">
         <v>1</v>
@@ -1264,10 +1264,10 @@
         <v>0.13</v>
       </c>
       <c r="M7" t="n">
-        <v>-0.06375</v>
+        <v>-0.0575</v>
       </c>
       <c r="N7" t="n">
-        <v>0.8912499999999998</v>
+        <v>0.7474999999999998</v>
       </c>
       <c r="O7" t="n">
         <v>1</v>
@@ -1391,10 +1391,10 @@
         <v>0.04</v>
       </c>
       <c r="M8" t="n">
-        <v>-0.03875000000000001</v>
+        <v>-0.01249999999999999</v>
       </c>
       <c r="N8" t="n">
-        <v>1.7775</v>
+        <v>2.1175</v>
       </c>
       <c r="O8" t="n">
         <v>1</v>
@@ -1518,7 +1518,7 @@
         <v>0.12</v>
       </c>
       <c r="M9" t="n">
-        <v>0.01625</v>
+        <v>0.01625000000000001</v>
       </c>
       <c r="N9" t="n">
         <v>3.24125</v>
@@ -1645,7 +1645,7 @@
         <v>0.11</v>
       </c>
       <c r="M10" t="n">
-        <v>0.04</v>
+        <v>0.04000000000000001</v>
       </c>
       <c r="N10" t="n">
         <v>3.5375</v>
@@ -1772,7 +1772,7 @@
         <v>0.05</v>
       </c>
       <c r="M11" t="n">
-        <v>0.01875000000000001</v>
+        <v>0.01875</v>
       </c>
       <c r="N11" t="n">
         <v>3.38625</v>
@@ -1899,10 +1899,10 @@
         <v>0.03</v>
       </c>
       <c r="M12" t="n">
-        <v>0.01375000000000001</v>
+        <v>0.01375</v>
       </c>
       <c r="N12" t="n">
-        <v>3.41375</v>
+        <v>3.413749999999999</v>
       </c>
       <c r="O12" t="n">
         <v>1</v>
@@ -9834,6 +9834,133 @@
       </c>
       <c r="AM74" t="n">
         <v>115.1</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>4406</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>115.2Q</t>
+        </is>
+      </c>
+      <c r="C75" t="n">
+        <v>28</v>
+      </c>
+      <c r="D75" t="n">
+        <v>29</v>
+      </c>
+      <c r="E75" t="n">
+        <v>-1</v>
+      </c>
+      <c r="F75" t="n">
+        <v>-3.33</v>
+      </c>
+      <c r="G75" t="n">
+        <v>-13</v>
+      </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>-46.77%</t>
+        </is>
+      </c>
+      <c r="I75" t="n">
+        <v>8</v>
+      </c>
+      <c r="J75" t="n">
+        <v>-6</v>
+      </c>
+      <c r="K75" t="n">
+        <v>-6</v>
+      </c>
+      <c r="L75" t="n">
+        <v>-0.11</v>
+      </c>
+      <c r="M75" t="n">
+        <v>-0.24125</v>
+      </c>
+      <c r="N75" t="n">
+        <v>-5.03375</v>
+      </c>
+      <c r="O75" t="n">
+        <v>1</v>
+      </c>
+      <c r="P75" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q75" t="n">
+        <v>0</v>
+      </c>
+      <c r="R75" t="n">
+        <v>0</v>
+      </c>
+      <c r="S75" t="n">
+        <v>1</v>
+      </c>
+      <c r="T75" t="n">
+        <v>0</v>
+      </c>
+      <c r="U75" t="n">
+        <v>0</v>
+      </c>
+      <c r="V75" t="n">
+        <v>115.2</v>
+      </c>
+      <c r="W75" t="n">
+        <v>0.21</v>
+      </c>
+      <c r="X75" t="n">
+        <v>-0.65625</v>
+      </c>
+      <c r="Y75" t="n">
+        <v>2.72</v>
+      </c>
+      <c r="Z75" t="n">
+        <v>-0.4495867768595041</v>
+      </c>
+      <c r="AA75" t="n">
+        <v>0.58</v>
+      </c>
+      <c r="AB75" t="n">
+        <v>-0.8405797101449275</v>
+      </c>
+      <c r="AC75" t="n">
+        <v>0.1699999999999999</v>
+      </c>
+      <c r="AD75" t="n">
+        <v>-0.0485714285714286</v>
+      </c>
+      <c r="AE75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AG75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AH75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AI75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AJ75" t="inlineStr">
+        <is>
+          <t>EPS成長 / 毛利率成長</t>
+        </is>
+      </c>
+      <c r="AK75" t="n">
+        <v>115</v>
+      </c>
+      <c r="AL75" t="n">
+        <v>2</v>
+      </c>
+      <c r="AM75" t="n">
+        <v>115.2</v>
       </c>
     </row>
   </sheetData>
